--- a/docs/apresentacao/resultados_ssl.xlsx
+++ b/docs/apresentacao/resultados_ssl.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="resumo_metodos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="regimes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="encoder_x_tecnica" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="cross_encoder" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="comb2target" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="regimes_finetune" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="regimes_linear" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="encoder_x_tecnica" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="cross_encoder" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="comb2target" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,15 +423,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,31 +492,43 @@
           <t>SL (from scratch)</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>71.28 ± 1.80</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>46.26 ± 0.30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>76.59 ± 0.76</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>64.45 ± 2.50</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>36.52 ± 0.56</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>73.42 ± 1.12</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -524,32 +538,44 @@
           <t>LFR (linear)</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>72</v>
-      </c>
-      <c r="C3" t="n">
-        <v>45</v>
-      </c>
-      <c r="D3" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="E3" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="G3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-2.8</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>71.99 ± 0.33</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>45.00 ± 0.68</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>73.74 ± 0.38</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>65.69 ± 0.64</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>35.81 ± 0.46</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>71.54 ± 0.34</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="4">
@@ -558,32 +584,44 @@
           <t>LFR (finetune)</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="E4" t="n">
-        <v>67</v>
-      </c>
-      <c r="F4" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.3</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>73.26 ± 1.92</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>46.46 ± 1.30</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>77.86 ± 1.27</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>66.97 ± 2.27</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>36.72 ± 1.18</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>75.42 ± 1.57</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="5">
@@ -592,32 +630,44 @@
           <t>TF-C (linear)</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="C5" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>63</v>
-      </c>
-      <c r="F5" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-4.8</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>68.82 ± 1.10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>46.51 ± 0.36</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>71.76 ± 1.05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>63.04 ± 1.14</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>37.49 ± 0.52</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>69.50 ± 1.39</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>-4.83</v>
       </c>
     </row>
     <row r="6">
@@ -626,32 +676,44 @@
           <t>TF-C (finetune)</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="F6" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.2</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>80.21 ± 0.48</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>49.28 ± 0.30</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>82.82 ± 0.38</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>74.40 ± 0.33</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>40.62 ± 0.45</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>81.74 ± 0.43</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>6.24</v>
       </c>
     </row>
   </sheetData>
@@ -665,33 +727,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cenário</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Linha</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Acc 1-shot (%)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Acc 10-shot (%)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Acc 100-shot (%)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc 100% (%)</t>
         </is>
@@ -700,118 +773,256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cross-domain — LFR</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>46.5</v>
+          <t>In-domain</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>41.87 ± 2.51</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>58.20 ± 1.14</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>74.00 ± 1.57</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>76.59 ± 0.76</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cross-domain — SL</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="D3" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>46.3</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LFR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>43.10 ± 4.15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>62.39 ± 1.42</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>74.48 ± 1.25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>77.86 ± 1.27</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cross-domain — TF-C</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>49.3</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TF-C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>44.69 ± 4.36</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>70.36 ± 0.73</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>79.87 ± 0.58</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>82.82 ± 0.38</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>In-domain — LFR</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>77.90000000000001</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Δ LFR−SL (pp)</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>In-domain — SL</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="C6" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>74</v>
-      </c>
-      <c r="E6" t="n">
-        <v>76.59999999999999</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Δ TF-C−SL (pp)</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>6.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>In-domain — TF-C</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="D7" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="E7" t="n">
-        <v>82.8</v>
+          <t>Cross-domain</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>32.09 ± 2.06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>39.88 ± 0.92</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>44.92 ± 0.66</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>46.26 ± 0.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LFR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33.21 ± 3.05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>41.95 ± 0.97</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>45.59 ± 0.66</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>46.46 ± 1.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TF-C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>33.18 ± 2.65</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>45.41 ± 0.56</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>48.60 ± 0.72</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>49.28 ± 0.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Δ LFR−SL (pp)</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Δ TF-C−SL (pp)</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>3.02</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -822,187 +1033,302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cenário</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Acc SL (%)</t>
+          <t>Linha</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>F1 SL (%)</t>
+          <t>Acc 1-shot (%)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Acc LFR (%)</t>
+          <t>Acc 10-shot (%)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>F1 LFR (%)</t>
+          <t>Acc 100-shot (%)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Acc TF-C (%)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>F1 TF-C (%)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Δ Acc LFR−SL (pp)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Δ Acc TF-C−SL (pp)</t>
+          <t>Acc 100% (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CNN-PFF</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="F2" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="G2" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
+          <t>In-domain</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>41.87 ± 2.51</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>58.20 ± 1.14</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>74.00 ± 1.57</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>76.59 ± 0.76</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ResNet-SE-5</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="C3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.1</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LFR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>38.59 ± 2.73</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>48.81 ± 2.32</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>67.44 ± 0.39</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>73.74 ± 0.38</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BiGRU (RNN)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="C4" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="D4" t="n">
-        <v>73</v>
-      </c>
-      <c r="E4" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>13.6</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TF-C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>29.84 ± 2.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>58.76 ± 1.31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>70.55 ± 0.48</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>71.76 ± 1.05</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TS-TCC</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="C5" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="D5" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="F5" t="n">
-        <v>80</v>
-      </c>
-      <c r="G5" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.2</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Δ LFR−SL (pp)</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>-6.56</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Δ TF-C−SL (pp)</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-12.03</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>-4.83</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cross-domain</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>32.09 ± 2.06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>39.88 ± 0.92</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>44.92 ± 0.66</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>46.26 ± 0.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LFR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>31.34 ± 3.31</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>35.42 ± 2.61</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>43.03 ± 0.41</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>45.00 ± 0.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TF-C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>23.23 ± 0.47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>39.95 ± 0.78</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>45.54 ± 0.50</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>46.51 ± 0.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Δ LFR−SL (pp)</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Δ TF-C−SL (pp)</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1017,14 +1343,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1075,29 +1401,41 @@
           <t>CNN-PFF</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="F2" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>79.55 ± 0.91</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>77.36 ± 1.43</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>75.69 ± 4.25</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>73.35 ± 4.74</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>85.58 ± 0.41</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>84.92 ± 0.32</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>6.03</v>
       </c>
     </row>
     <row r="3">
@@ -1106,29 +1444,41 @@
           <t>ResNet-SE-5</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="C3" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="D3" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.6</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>80.36 ± 1.52</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>78.33 ± 1.91</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>80.86 ± 2.74</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>79.44 ± 3.61</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>82.45 ± 0.53</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>81.05 ± 0.61</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -1137,29 +1487,41 @@
           <t>BiGRU (RNN)</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.2</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>69.61 ± 0.34</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>63.59 ± 0.52</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>72.99 ± 0.97</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>67.82 ± 0.69</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>83.23 ± 0.72</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>82.73 ± 0.86</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>13.61</v>
       </c>
     </row>
     <row r="5">
@@ -1168,29 +1530,41 @@
           <t>TS-TCC</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.2</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>76.82 ± 1.63</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>74.41 ± 2.24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>81.89 ± 1.42</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>81.06 ± 1.59</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>80.03 ± 0.53</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>78.26 ± 0.91</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>3.21</v>
       </c>
     </row>
   </sheetData>
@@ -1204,16 +1578,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Acc SL (%)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>F1 SL (%)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Acc LFR (%)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>F1 LFR (%)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Acc TF-C (%)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>F1 TF-C (%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Δ Acc LFR−SL (pp)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Δ Acc TF-C−SL (pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CNN-PFF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>46.45 ± 0.43</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>36.50 ± 0.32</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>45.63 ± 2.61</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>35.82 ± 2.62</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>51.43 ± 1.30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>42.71 ± 1.19</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ResNet-SE-5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>46.88 ± 0.81</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>37.72 ± 1.28</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>47.58 ± 0.81</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>38.45 ± 0.71</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>48.51 ± 0.69</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>39.83 ± 0.93</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BiGRU (RNN)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>44.38 ± 0.42</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>34.70 ± 0.42</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>45.07 ± 1.46</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>34.45 ± 1.31</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>49.61 ± 0.90</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>41.30 ± 0.99</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TS-TCC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>47.33 ± 0.67</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>37.17 ± 0.93</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>47.58 ± 0.83</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>38.15 ± 1.20</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>47.56 ± 0.77</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>38.65 ± 0.75</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1244,10 +1858,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Δ vs SL (pp)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Δ pré-treino multi (pp)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Δ rótulos misturados (pp)</t>
         </is>
@@ -1256,7 +1875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LFR</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1264,20 +1883,31 @@
           <t>KuHar</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.2</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>64.36 ± 2.69</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>62.21 ± 1.81</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="3">
@@ -1286,20 +1916,31 @@
           <t>MotionSense</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>86</v>
-      </c>
-      <c r="E3" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-5.6</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>81.22 ± 1.98</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>76.46 ± 3.33</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>-4.75</v>
       </c>
     </row>
     <row r="4">
@@ -1308,20 +1949,31 @@
           <t>RealWorld_thigh</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="D4" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>70</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.7</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>69.76 ± 0.56</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>67.98 ± 1.24</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="5">
@@ -1330,20 +1982,31 @@
           <t>RealWorld_waist</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>72</v>
-      </c>
-      <c r="D5" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-1.7</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>71.15 ± 0.70</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>68.85 ± 1.28</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="6">
@@ -1352,20 +2015,31 @@
           <t>UCI</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-11.7</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>89.91 ± 0.21</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>77.73 ± 2.73</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>-12.18</v>
       </c>
     </row>
     <row r="7">
@@ -1374,163 +2048,515 @@
           <t>WISDM</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>86</v>
-      </c>
-      <c r="D7" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="E7" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>83.12 ± 0.60</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>74.44 ± 2.00</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
-        <v>-9.300000000000001</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>-8.67</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TF-C</t>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Média (todos)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>76.59 ± 0.76</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71.28 ± 1.80</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>-5.31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LFR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>KuHar</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MotionSense</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="D9" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="E9" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-4.1</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>62.06 ± 7.37</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>58.54 ± 3.70</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>61.72 ± 2.13</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>3.17</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>RealWorld_thigh</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="D10" t="n">
-        <v>74</v>
-      </c>
-      <c r="E10" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.8</v>
+          <t>MotionSense</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>85.80 ± 1.16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86.05 ± 1.59</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>80.44 ± 1.08</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>-5.61</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>RealWorld_waist</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="E11" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.3</v>
+          <t>RealWorld_thigh</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>69.75 ± 0.34</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>68.23 ± 0.59</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>69.96 ± 2.70</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>UCI</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="E12" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-5.5</v>
+          <t>RealWorld_waist</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>72.04 ± 1.85</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>72.16 ± 0.75</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>70.50 ± 1.68</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
+          <t>UCI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>91.46 ± 0.39</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>91.91 ± 0.41</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>80.20 ± 3.26</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>-11.72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
           <t>WISDM</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="D13" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="E13" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-7.3</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>86.03 ± 0.55</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>86.08 ± 0.62</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>76.73 ± 2.64</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>-9.34</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Média (todos)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>77.86 ± 1.27</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>77.16 ± 0.76</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>73.26 ± 1.92</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TF-C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KuHar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>75.49 ± 0.41</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>77.39 ± 2.00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>73.19 ± 2.09</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MotionSense</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>89.89 ± 1.98</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>90.92 ± 1.05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>86.81 ± 1.38</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>-4.11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RealWorld_thigh</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>72.83 ± 3.13</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>74.03 ± 1.00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>76.82 ± 0.87</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RealWorld_waist</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>76.30 ± 2.21</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>75.71 ± 0.99</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>75.44 ± 0.57</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UCI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>94.72 ± 0.16</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>92.94 ± 0.84</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>87.47 ± 1.08</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>-5.47</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WISDM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>87.72 ± 0.40</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>88.84 ± 0.40</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>81.52 ± 0.42</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>-7.32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Média (todos)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>82.82 ± 0.38</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>83.31 ± 0.18</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>80.21 ± 0.48</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>-3.1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A2:A7"/>
+  <mergeCells count="3">
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A16:A22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
